--- a/output/pdf_financials_xlsx/OYL.xlsx
+++ b/output/pdf_financials_xlsx/OYL.xlsx
@@ -1291,16 +1291,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>6.678561</v>
+        <v>-6.678561</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3.692712</v>
+        <v>-3.692712</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4.740489</v>
+        <v>-4.740489</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6.78533</v>
+        <v>-6.78533</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-152.224578</v>
@@ -1309,16 +1309,16 @@
         <v>0.599207</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>45.001229</v>
+        <v>-45.001229</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>26.277116</v>
+        <v>-26.277116</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.017941</v>
+        <v>-5.017941</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>5.70759</v>
+        <v>-5.70759</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-6.056361</v>
@@ -1591,16 +1591,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6.678561</v>
+        <v>-6.678561</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.692712</v>
+        <v>-3.692712</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4.740489</v>
+        <v>-4.740489</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>6.78533</v>
+        <v>-6.78533</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-152.224578</v>
@@ -1609,16 +1609,16 @@
         <v>0.599207</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>45.001229</v>
+        <v>-45.001229</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>26.277116</v>
+        <v>-26.277116</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.017941</v>
+        <v>-5.017941</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>5.70759</v>
+        <v>-5.70759</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-6.056361</v>
@@ -1765,16 +1765,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6.678561</v>
+        <v>-6.678561</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.692712</v>
+        <v>-3.692712</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4.740489</v>
+        <v>-4.740489</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6.78533</v>
+        <v>-6.78533</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-152.224578</v>
@@ -1783,16 +1783,16 @@
         <v>0.599207</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>45.001229</v>
+        <v>-45.001229</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>26.277116</v>
+        <v>-26.277116</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5.017941</v>
+        <v>-5.017941</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5.70759</v>
+        <v>-5.70759</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-6.056361</v>
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>133.57122</v>
+        <v>-133.57122</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>123.0904</v>
+        <v>-123.0904</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>158.0163</v>
+        <v>-158.0163</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -2037,16 +2037,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6.678561</v>
+        <v>-6.678561</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.692712</v>
+        <v>-3.692712</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.740489</v>
+        <v>-4.740489</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6.78533</v>
+        <v>-6.78533</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-152.224578</v>
@@ -2055,16 +2055,16 @@
         <v>0.599207</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>45.001229</v>
+        <v>-45.001229</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>26.277116</v>
+        <v>-26.277116</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.017941</v>
+        <v>-5.017941</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>5.70759</v>
+        <v>-5.70759</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-6.056361</v>
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.678561</v>
+        <v>-6.678561</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.692712</v>
+        <v>-3.692712</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.740489</v>
+        <v>-4.740489</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6.78533</v>
+        <v>-6.78533</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-152.224578</v>
@@ -2171,16 +2171,16 @@
         <v>0.599207</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>45.001229</v>
+        <v>-45.001229</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>26.277116</v>
+        <v>-26.277116</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5.017941</v>
+        <v>-5.017941</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>5.70759</v>
+        <v>-5.70759</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-6.056361</v>
@@ -2303,16 +2303,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -2321,16 +2321,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -7437,49 +7437,49 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-5.736931</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-25.002618</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-56.224064</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-17.930083</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>33.96326</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-2.59563</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-1.365429</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-3.000742</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.970447</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>13.817126</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-46.96022</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-54.017882</v>
       </c>
       <c r="P118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.17624</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.176457</v>
       </c>
     </row>
     <row r="119">
@@ -20369,7 +20369,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -22466,7 +22470,11 @@
           <t>Impairment of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -22866,7 +22874,11 @@
           <t>Purchases of exploration and evaluation expenditures 9</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -23676,7 +23688,11 @@
           <t>Impairment of exploration and evaluation expenditures 9</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -23977,7 +23993,11 @@
           <t>Purchases of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -25292,7 +25312,11 @@
           <t>Recovery of previously impaired exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -26395,7 +26419,11 @@
           <t>Purchases of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -26484,7 +26512,11 @@
           <t>Proceeds from disposition of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -27648,7 +27680,11 @@
           <t>Settlement of related party debt on disposition of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -30042,7 +30078,11 @@
           <t>Additions to exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -30533,7 +30573,11 @@
           <t>Impairment of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -31545,7 +31589,11 @@
           <t>Impairment of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -32343,7 +32391,11 @@
           <t>Impairment of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -40925,13 +40977,13 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>4.740489</v>
+        <v>-4.740489</v>
       </c>
       <c r="H326" s="5" t="n">
-        <v>6.78533</v>
+        <v>-6.78533</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>152.224578</v>
+        <v>-152.224578</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
@@ -40949,13 +41001,13 @@
         </is>
       </c>
       <c r="M326" s="5" t="n">
-        <v>5.017941</v>
+        <v>-5.017941</v>
       </c>
       <c r="N326" s="5" t="n">
-        <v>5.70759</v>
+        <v>-5.70759</v>
       </c>
       <c r="O326" s="5" t="n">
-        <v>6.056361</v>
+        <v>-6.056361</v>
       </c>
       <c r="P326" t="inlineStr">
         <is>
@@ -44018,13 +44070,13 @@
         </is>
       </c>
       <c r="K357" s="5" t="n">
-        <v>45.001229</v>
+        <v>-45.001229</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>26.277116</v>
+        <v>-26.277116</v>
       </c>
       <c r="M357" s="5" t="n">
-        <v>5.017941</v>
+        <v>-5.017941</v>
       </c>
       <c r="N357" t="inlineStr">
         <is>
@@ -46989,10 +47041,10 @@
         </is>
       </c>
       <c r="F387" s="5" t="n">
-        <v>3.692712</v>
+        <v>-3.692712</v>
       </c>
       <c r="G387" s="5" t="n">
-        <v>4.740489</v>
+        <v>-4.740489</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -47899,10 +47951,10 @@
         </is>
       </c>
       <c r="E396" s="5" t="n">
-        <v>6.678561</v>
+        <v>-6.678561</v>
       </c>
       <c r="F396" s="5" t="n">
-        <v>3.692712</v>
+        <v>-3.692712</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OYL.xlsx
+++ b/output/pdf_financials_xlsx/OYL.xlsx
@@ -1059,31 +1059,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.467017</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.036472</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013692</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09773900000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.145213</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.050231</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035626</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005314</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0009810000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -2037,31 +2037,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.678561</v>
+        <v>-6.211544</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.692712</v>
+        <v>-3.65624</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.740489</v>
+        <v>-4.726797</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.78533</v>
+        <v>-6.687591</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-152.224578</v>
+        <v>-152.369791</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.599207</v>
+        <v>0.548976</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-45.001229</v>
+        <v>-44.965603</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-26.277116</v>
+        <v>-26.271802</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.017941</v>
+        <v>-5.01696</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-5.70759</v>
@@ -2153,31 +2153,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.678561</v>
+        <v>-6.211544</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.692712</v>
+        <v>-3.65624</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.740489</v>
+        <v>-4.726797</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.78533</v>
+        <v>-6.687591</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-152.224578</v>
+        <v>-152.369791</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.599207</v>
+        <v>0.548976</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-45.001229</v>
+        <v>-44.965603</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-26.277116</v>
+        <v>-26.271802</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.017941</v>
+        <v>-5.01696</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-5.70759</v>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -39963,7 +39963,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -41460,7 +41460,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -43258,7 +43258,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -43551,7 +43551,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -47739,7 +47739,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E394" s="5" t="n">

--- a/output/pdf_financials_xlsx/OYL.xlsx
+++ b/output/pdf_financials_xlsx/OYL.xlsx
@@ -7550,25 +7550,25 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.924</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>39.221385</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>84.722926</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>0.005446</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>-0.026785</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>-0.0226</v>
       </c>
       <c r="J120" s="3" t="n">
         <v>0</v>
@@ -30983,7 +30983,11 @@
           <t>Issuance of Common Shares (net of issuance costs)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -31890,7 +31894,11 @@
           <t>Issuance of common shares (net of issuance costs)</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -34797,7 +34805,11 @@
           <t>Issuances of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OYL.xlsx
+++ b/output/pdf_financials_xlsx/OYL.xlsx
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>0.761749</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0</v>
+        <v>0.211939</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>0</v>
@@ -2902,10 +2902,10 @@
         <v>0</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.761749</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>0.211939</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0.18817</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>12.048734</v>
+        <v>11.286985</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>12.633104</v>
+        <v>12.421165</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>2.214842</v>
